--- a/lab2/таблица_регистра_37.xlsx
+++ b/lab2/таблица_регистра_37.xlsx
@@ -54,7 +54,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +98,13 @@
       <color rgb="FF7F6000"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -320,6 +327,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCFE2F3"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -363,12 +376,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,21 +694,18 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -710,37 +714,37 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -752,77 +756,80 @@
     <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -861,11 +868,14 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1528,13 +1538,13 @@
       <c r="AB2" s="3">
         <v>14</v>
       </c>
-      <c r="AC2" s="5">
+      <c r="AC2" s="3">
         <v>13</v>
       </c>
       <c r="AD2" s="12">
         <v>12</v>
       </c>
-      <c r="AE2" s="5">
+      <c r="AE2" s="14">
         <v>11</v>
       </c>
       <c r="AF2" s="12">
@@ -1558,16 +1568,16 @@
       <c r="AL2" s="3">
         <v>4</v>
       </c>
-      <c r="AM2" s="5">
+      <c r="AM2" s="14">
         <v>3</v>
       </c>
       <c r="AN2" s="12">
         <v>2</v>
       </c>
-      <c r="AO2" s="14">
-        <v>1</v>
-      </c>
-      <c r="AP2" s="15"/>
+      <c r="AO2" s="15">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="16"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="2:42">
       <c r="B3" s="6" t="s">
@@ -1690,7 +1700,7 @@
       <c r="AO3" s="7">
         <v>1</v>
       </c>
-      <c r="AP3" s="16">
+      <c r="AP3" s="17">
         <f t="shared" ref="AP3:AP63" si="0">IF(_xlfn.XOR(E3,AD3,AF3,AN3),1,0)</f>
         <v>0</v>
       </c>
@@ -1852,7 +1862,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP4" s="16">
+      <c r="AP4" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2014,7 +2024,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP5" s="16">
+      <c r="AP5" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2176,7 +2186,7 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AP6" s="16">
+      <c r="AP6" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2338,7 +2348,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AP7" s="16">
+      <c r="AP7" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2500,7 +2510,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AP8" s="16">
+      <c r="AP8" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2662,7 +2672,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AP9" s="16">
+      <c r="AP9" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2824,7 +2834,7 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="AP10" s="16">
+      <c r="AP10" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2986,7 +2996,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AP11" s="16">
+      <c r="AP11" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3148,7 +3158,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="16">
+      <c r="AP12" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3310,7 +3320,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AP13" s="16">
+      <c r="AP13" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3472,7 +3482,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP14" s="16">
+      <c r="AP14" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3634,7 +3644,7 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="16">
+      <c r="AP15" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3796,7 +3806,7 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AP16" s="16">
+      <c r="AP16" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3958,7 +3968,7 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AP17" s="16">
+      <c r="AP17" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4120,7 +4130,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="16">
+      <c r="AP18" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4282,7 +4292,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="16">
+      <c r="AP19" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4444,7 +4454,7 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AP20" s="16">
+      <c r="AP20" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4606,7 +4616,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AP21" s="16">
+      <c r="AP21" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4768,7 +4778,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AP22" s="16">
+      <c r="AP22" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4930,7 +4940,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="16">
+      <c r="AP23" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -5092,7 +5102,7 @@
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="AP24" s="16">
+      <c r="AP24" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -5254,7 +5264,7 @@
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="AP25" s="16">
+      <c r="AP25" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5416,7 +5426,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AP26" s="16">
+      <c r="AP26" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5578,7 +5588,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP27" s="16">
+      <c r="AP27" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -5740,7 +5750,7 @@
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
-      <c r="AP28" s="16">
+      <c r="AP28" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -5902,7 +5912,7 @@
         <f t="shared" si="26"/>
         <v>1</v>
       </c>
-      <c r="AP29" s="16">
+      <c r="AP29" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6064,7 +6074,7 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AP30" s="16">
+      <c r="AP30" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6226,7 +6236,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AP31" s="16">
+      <c r="AP31" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6388,7 +6398,7 @@
         <f t="shared" si="29"/>
         <v>1</v>
       </c>
-      <c r="AP32" s="16">
+      <c r="AP32" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6550,7 +6560,7 @@
         <f t="shared" si="30"/>
         <v>1</v>
       </c>
-      <c r="AP33" s="16">
+      <c r="AP33" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6712,7 +6722,7 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="AP34" s="16">
+      <c r="AP34" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6874,7 +6884,7 @@
         <f t="shared" si="32"/>
         <v>1</v>
       </c>
-      <c r="AP35" s="16">
+      <c r="AP35" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -7036,7 +7046,7 @@
         <f t="shared" si="33"/>
         <v>1</v>
       </c>
-      <c r="AP36" s="16">
+      <c r="AP36" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -7198,7 +7208,7 @@
         <f t="shared" si="34"/>
         <v>1</v>
       </c>
-      <c r="AP37" s="16">
+      <c r="AP37" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -7360,7 +7370,7 @@
         <f t="shared" si="35"/>
         <v>1</v>
       </c>
-      <c r="AP38" s="16">
+      <c r="AP38" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -7522,7 +7532,7 @@
         <f t="shared" si="36"/>
         <v>1</v>
       </c>
-      <c r="AP39" s="16">
+      <c r="AP39" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -7684,7 +7694,7 @@
         <f t="shared" si="37"/>
         <v>1</v>
       </c>
-      <c r="AP40" s="16">
+      <c r="AP40" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7846,7 +7856,7 @@
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AP41" s="16">
+      <c r="AP41" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8008,7 +8018,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AP42" s="16">
+      <c r="AP42" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8170,7 +8180,7 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="AP43" s="16">
+      <c r="AP43" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -8332,7 +8342,7 @@
         <f t="shared" si="41"/>
         <v>1</v>
       </c>
-      <c r="AP44" s="16">
+      <c r="AP44" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8494,7 +8504,7 @@
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="AP45" s="16">
+      <c r="AP45" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -8656,7 +8666,7 @@
         <f t="shared" si="43"/>
         <v>1</v>
       </c>
-      <c r="AP46" s="16">
+      <c r="AP46" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -8818,7 +8828,7 @@
         <f t="shared" si="44"/>
         <v>1</v>
       </c>
-      <c r="AP47" s="16">
+      <c r="AP47" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8980,7 +8990,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="AP48" s="16">
+      <c r="AP48" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -9142,7 +9152,7 @@
         <f t="shared" si="46"/>
         <v>1</v>
       </c>
-      <c r="AP49" s="16">
+      <c r="AP49" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -9304,7 +9314,7 @@
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
-      <c r="AP50" s="16">
+      <c r="AP50" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -9466,7 +9476,7 @@
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="AP51" s="16">
+      <c r="AP51" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -9628,7 +9638,7 @@
         <f t="shared" si="49"/>
         <v>1</v>
       </c>
-      <c r="AP52" s="16">
+      <c r="AP52" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -9790,7 +9800,7 @@
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="AP53" s="16">
+      <c r="AP53" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -9952,7 +9962,7 @@
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="AP54" s="16">
+      <c r="AP54" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10114,7 +10124,7 @@
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="AP55" s="16">
+      <c r="AP55" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10276,7 +10286,7 @@
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AP56" s="16">
+      <c r="AP56" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -10438,7 +10448,7 @@
         <f t="shared" si="54"/>
         <v>1</v>
       </c>
-      <c r="AP57" s="16">
+      <c r="AP57" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -10600,7 +10610,7 @@
         <f t="shared" si="55"/>
         <v>1</v>
       </c>
-      <c r="AP58" s="16">
+      <c r="AP58" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -10762,7 +10772,7 @@
         <f t="shared" si="56"/>
         <v>1</v>
       </c>
-      <c r="AP59" s="16">
+      <c r="AP59" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -10924,7 +10934,7 @@
         <f t="shared" si="57"/>
         <v>1</v>
       </c>
-      <c r="AP60" s="16">
+      <c r="AP60" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -11086,7 +11096,7 @@
         <f t="shared" si="58"/>
         <v>1</v>
       </c>
-      <c r="AP61" s="16">
+      <c r="AP61" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -11248,7 +11258,7 @@
         <f t="shared" si="59"/>
         <v>1</v>
       </c>
-      <c r="AP62" s="16">
+      <c r="AP62" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -11409,7 +11419,7 @@
         <f t="shared" si="60"/>
         <v>1</v>
       </c>
-      <c r="AP63" s="16">
+      <c r="AP63" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
